--- a/database/controller_excel/FO-DSP-TI-01 Resguardo de herramientas TI Rev.00.xlsx
+++ b/database/controller_excel/FO-DSP-TI-01 Resguardo de herramientas TI Rev.00.xlsx
@@ -5,21 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dspt2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Inventario_TI\database\controller_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="3795" windowHeight="2700"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="3792" windowHeight="2700"/>
   </bookViews>
   <sheets>
     <sheet name="Resguardo Hta" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -190,7 +190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -347,11 +347,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -394,14 +435,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -441,13 +475,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -466,6 +493,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,109 +765,112 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="6" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" customWidth="1"/>
+    <col min="11" max="11" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="36" t="s">
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="37"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="34"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="36" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="37"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="34"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="37"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="34"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="38"/>
-    </row>
-    <row r="6" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="35"/>
+    </row>
+    <row r="6" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="39"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="26"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
       <c r="I8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="4"/>
       <c r="C9" s="8"/>
@@ -833,7 +882,7 @@
       <c r="I9" s="4"/>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
@@ -847,48 +896,48 @@
       </c>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -899,7 +948,7 @@
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
@@ -910,57 +959,57 @@
       <c r="D16" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="42" t="s">
+      <c r="F16" s="34"/>
+      <c r="G16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="42" t="s">
+      <c r="H16" s="34"/>
+      <c r="I16" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="37"/>
+      <c r="J16" s="34"/>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="37"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="37"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="37"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="54"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="48"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="48"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -972,205 +1021,207 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
-      <c r="B21" s="46" t="s">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-    </row>
-    <row r="22" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="49" t="s">
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+    </row>
+    <row r="22" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
-      <c r="B24" s="49" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="49" t="s">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
-      <c r="B26" s="49" t="s">
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="49" t="s">
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-    </row>
-    <row r="28" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="24"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-    </row>
-    <row r="29" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+    </row>
+    <row r="28" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+    </row>
+    <row r="29" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="47" t="s">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="H32" s="48" t="s">
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="H32" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C36" s="47" t="s">
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="H36" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C37" s="47" t="s">
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="H36" s="41">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="H37" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-    </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="H37" s="41">
+        <f>C10</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="34">

--- a/database/controller_excel/FO-DSP-TI-01 Resguardo de herramientas TI Rev.00.xlsx
+++ b/database/controller_excel/FO-DSP-TI-01 Resguardo de herramientas TI Rev.00.xlsx
@@ -449,6 +449,55 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
@@ -457,61 +506,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -781,73 +781,73 @@
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="45"/>
+      <c r="C2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="33" t="s">
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="34"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="33" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="33" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="35"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="36"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
@@ -859,12 +859,12 @@
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="2" t="s">
         <v>6</v>
       </c>
@@ -901,41 +901,41 @@
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
@@ -959,55 +959,55 @@
       <c r="D16" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="39" t="s">
+      <c r="F16" s="44"/>
+      <c r="G16" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="39" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="34"/>
+      <c r="J16" s="44"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="54"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="38"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="48"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="33"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="48"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="33"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
@@ -1023,17 +1023,17 @@
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
@@ -1049,99 +1049,99 @@
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20"/>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
     </row>
     <row r="28" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
     </row>
     <row r="29" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22"/>
@@ -1163,16 +1163,16 @@
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="H32" s="42" t="s">
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="H32" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1185,30 +1185,27 @@
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="H36" s="41">
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="H36" s="27">
         <f>C8</f>
         <v>0</v>
       </c>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="41" t="s">
+      <c r="C37" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="H37" s="41">
-        <f>C10</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H38" s="22"/>
@@ -1225,6 +1222,29 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:H4"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C5:J6"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B12:J14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="H32:J32"/>
     <mergeCell ref="C36:E36"/>
     <mergeCell ref="H36:J36"/>
     <mergeCell ref="C37:E37"/>
@@ -1236,29 +1256,6 @@
     <mergeCell ref="B27:J27"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="B29:J29"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="B12:J14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:H4"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C5:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
